--- a/Output/Tables/table1_by_PHC_org.xlsx
+++ b/Output/Tables/table1_by_PHC_org.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -351,27 +351,27 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>[ALL]   N=2058</t>
+          <t>[ALL]   N=1963</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Equip_Atdom   N=743</t>
+          <t>Equip_Atdom   N=714</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Equip_Inf   N=299</t>
+          <t>Equip_Inf   N=260</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>UAB_consulta   N=367</t>
+          <t>UAB_consulta   N=353</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>UAB_consulta_reforc   N=649</t>
+          <t>UAB_consulta_reforc   N=636</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -388,32 +388,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1573 (76.4%)  </t>
+          <t xml:space="preserve">  1490 (75.9%)  </t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  585 (78.7%)   </t>
+          <t xml:space="preserve">  557 (78.0%)   </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  226 (75.6%)   </t>
+          <t xml:space="preserve">  194 (74.6%)   </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  272 (74.1%)   </t>
+          <t xml:space="preserve">  261 (73.9%)   </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    490 (75.5%)    </t>
+          <t xml:space="preserve">    478 (75.2%)    </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.294  </t>
+          <t xml:space="preserve">  0.406  </t>
         </is>
       </c>
     </row>
@@ -425,32 +425,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1475 (71.7%)  </t>
+          <t xml:space="preserve">  1397 (71.2%)  </t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  530 (71.3%)   </t>
+          <t xml:space="preserve">  509 (71.3%)   </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  235 (78.6%)   </t>
+          <t xml:space="preserve">  199 (76.5%)   </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  241 (65.7%)   </t>
+          <t xml:space="preserve">  231 (65.4%)   </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    469 (72.3%)    </t>
+          <t xml:space="preserve">    458 (72.0%)    </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.003  </t>
+          <t xml:space="preserve">  0.023  </t>
         </is>
       </c>
     </row>
@@ -462,32 +462,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  88.7 (10.1)   </t>
+          <t xml:space="preserve">  88.7 (10.0)   </t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  88.3 (9.03)   </t>
+          <t xml:space="preserve">  88.3 (8.95)   </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  90.6 (8.08)   </t>
+          <t xml:space="preserve">  90.4 (8.19)   </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  88.1 (11.3)   </t>
+          <t xml:space="preserve">  88.3 (10.9)   </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    88.7 (11.1)    </t>
+          <t xml:space="preserve">    88.8 (11.2)    </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> &lt;0.001  </t>
+          <t xml:space="preserve">  0.029  </t>
         </is>
       </c>
     </row>
@@ -499,32 +499,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.19 (3.12)   </t>
+          <t xml:space="preserve">  3.17 (3.12)   </t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.03 (2.41)   </t>
+          <t xml:space="preserve">  3.05 (2.35)   </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.01 (2.33)   </t>
+          <t xml:space="preserve">  2.90 (2.18)   </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.44 (4.02)   </t>
+          <t xml:space="preserve">  3.42 (4.04)   </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3.31 (3.55)    </t>
+          <t xml:space="preserve">    3.28 (3.56)    </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.127  </t>
+          <t xml:space="preserve">  0.106  </t>
         </is>
       </c>
     </row>
@@ -536,32 +536,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1933 (93.9%)  </t>
+          <t xml:space="preserve">  1840 (93.7%)  </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  714 (96.1%)   </t>
+          <t xml:space="preserve">  685 (95.9%)   </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  283 (94.6%)   </t>
+          <t xml:space="preserve">  246 (94.6%)   </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  339 (92.4%)   </t>
+          <t xml:space="preserve">  325 (92.1%)   </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    597 (92.0%)    </t>
+          <t xml:space="preserve">    584 (91.8%)    </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.007  </t>
+          <t xml:space="preserve">  0.008  </t>
         </is>
       </c>
     </row>
@@ -573,27 +573,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  11.4 (4.55)   </t>
+          <t xml:space="preserve">  11.4 (4.56)   </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  12.1 (4.49)   </t>
+          <t xml:space="preserve">  12.0 (4.47)   </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  11.8 (4.19)   </t>
+          <t xml:space="preserve">  11.7 (4.12)   </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.9 (4.52)   </t>
+          <t xml:space="preserve">  10.9 (4.56)   </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    10.9 (4.71)    </t>
+          <t xml:space="preserve">    10.9 (4.73)    </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -615,22 +615,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  20.9 (8.06)   </t>
+          <t xml:space="preserve">  20.8 (8.01)   </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  19.2 (7.64)   </t>
+          <t xml:space="preserve">  19.2 (7.57)   </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  18.5 (8.10)   </t>
+          <t xml:space="preserve">  18.6 (8.17)   </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">    18.3 (8.33)    </t>
+          <t xml:space="preserve">    18.3 (8.38)    </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.38 (0.15)   </t>
+          <t xml:space="preserve">  0.37 (0.15)   </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.833  </t>
+          <t xml:space="preserve">  0.848  </t>
         </is>
       </c>
     </row>
@@ -684,27 +684,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1585 (77.0%)  </t>
+          <t xml:space="preserve">  1511 (77.0%)  </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  612 (82.4%)   </t>
+          <t xml:space="preserve">  587 (82.2%)   </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  167 (55.9%)   </t>
+          <t xml:space="preserve">  140 (53.8%)   </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  285 (77.7%)   </t>
+          <t xml:space="preserve">  273 (77.3%)   </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    521 (80.3%)    </t>
+          <t xml:space="preserve">    511 (80.3%)    </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -721,32 +721,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  162 (7.87%)   </t>
+          <t xml:space="preserve">  159 (8.10%)   </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   65 (8.75%)   </t>
+          <t xml:space="preserve">   64 (8.96%)   </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   31 (10.4%)   </t>
+          <t xml:space="preserve">   30 (11.5%)   </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   27 (7.36%)   </t>
+          <t xml:space="preserve">   27 (7.65%)   </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    39 (6.01%)     </t>
+          <t xml:space="preserve">    38 (5.97%)     </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.086  </t>
+          <t xml:space="preserve">  0.032  </t>
         </is>
       </c>
     </row>
@@ -795,27 +795,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  215 (10.4%)   </t>
+          <t xml:space="preserve">  204 (10.4%)   </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   70 (9.42%)   </t>
+          <t xml:space="preserve">   68 (9.52%)   </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   30 (10.0%)   </t>
+          <t xml:space="preserve">   24 (9.23%)   </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   41 (11.2%)   </t>
+          <t xml:space="preserve">   38 (10.8%)   </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">    74 (11.4%)     </t>
+          <t xml:space="preserve">    74 (11.6%)     </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -832,27 +832,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  261 (12.7%)   </t>
+          <t xml:space="preserve">  248 (12.6%)   </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   87 (11.7%)   </t>
+          <t xml:space="preserve">   85 (11.9%)   </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   42 (14.0%)   </t>
+          <t xml:space="preserve">   36 (13.8%)   </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   47 (12.8%)   </t>
+          <t xml:space="preserve">   45 (12.7%)   </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    85 (13.1%)     </t>
+          <t xml:space="preserve">    82 (12.9%)     </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -869,27 +869,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  476 (23.1%)   </t>
+          <t xml:space="preserve">  453 (23.1%)   </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  144 (19.4%)   </t>
+          <t xml:space="preserve">  138 (19.3%)   </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   80 (26.8%)   </t>
+          <t xml:space="preserve">   69 (26.5%)   </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   74 (20.2%)   </t>
+          <t xml:space="preserve">   71 (20.1%)   </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">    178 (27.4%)    </t>
+          <t xml:space="preserve">    175 (27.5%)    </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -906,27 +906,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1031 (50.1%)  </t>
+          <t xml:space="preserve">  988 (50.3%)   </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  430 (57.9%)   </t>
+          <t xml:space="preserve">  412 (57.7%)   </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  139 (46.5%)   </t>
+          <t xml:space="preserve">  125 (48.1%)   </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  178 (48.5%)   </t>
+          <t xml:space="preserve">  174 (49.3%)   </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    284 (43.8%)    </t>
+          <t xml:space="preserve">    277 (43.6%)    </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -943,27 +943,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   31 (1.51%)   </t>
+          <t xml:space="preserve">   29 (1.48%)   </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   6 (0.81%)    </t>
+          <t xml:space="preserve">   6 (0.84%)    </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   4 (1.34%)    </t>
+          <t xml:space="preserve">   3 (1.15%)    </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   8 (2.18%)    </t>
+          <t xml:space="preserve">   7 (1.98%)    </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">    13 (2.00%)     </t>
+          <t xml:space="preserve">    13 (2.04%)     </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -980,27 +980,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   44 (2.14%)   </t>
+          <t xml:space="preserve">   41 (2.09%)   </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   6 (0.81%)    </t>
+          <t xml:space="preserve">   5 (0.70%)    </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   4 (1.34%)    </t>
+          <t xml:space="preserve">   3 (1.15%)    </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   19 (5.18%)   </t>
+          <t xml:space="preserve">   18 (5.10%)   </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">    15 (2.31%)     </t>
+          <t xml:space="preserve">    15 (2.36%)     </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.004  </t>
+          <t xml:space="preserve">  0.003  </t>
         </is>
       </c>
     </row>
@@ -1054,27 +1054,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1095 (53.2%)  </t>
+          <t xml:space="preserve">  1052 (53.6%)  </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  400 (53.8%)   </t>
+          <t xml:space="preserve">  386 (54.1%)   </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  161 (53.8%)   </t>
+          <t xml:space="preserve">  142 (54.6%)   </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  193 (52.6%)   </t>
+          <t xml:space="preserve">  188 (53.3%)   </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">    341 (52.5%)    </t>
+          <t xml:space="preserve">    336 (52.8%)    </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1091,27 +1091,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  301 (14.6%)   </t>
+          <t xml:space="preserve">  289 (14.7%)   </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  119 (16.0%)   </t>
+          <t xml:space="preserve">  114 (16.0%)   </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">   38 (12.7%)   </t>
+          <t xml:space="preserve">   35 (13.5%)   </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">   50 (13.6%)   </t>
+          <t xml:space="preserve">   48 (13.6%)   </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">    94 (14.5%)     </t>
+          <t xml:space="preserve">    92 (14.5%)     </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1128,27 +1128,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  275 (13.4%)   </t>
+          <t xml:space="preserve">  257 (13.1%)   </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">   86 (11.6%)   </t>
+          <t xml:space="preserve">   80 (11.2%)   </t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">   44 (14.7%)   </t>
+          <t xml:space="preserve">   36 (13.8%)   </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">   50 (13.6%)   </t>
+          <t xml:space="preserve">   48 (13.6%)   </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">    95 (14.6%)     </t>
+          <t xml:space="preserve">    93 (14.6%)     </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1165,27 +1165,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  335 (16.3%)   </t>
+          <t xml:space="preserve">  316 (16.1%)   </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  131 (17.6%)   </t>
+          <t xml:space="preserve">  128 (17.9%)   </t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">   49 (16.4%)   </t>
+          <t xml:space="preserve">   41 (15.8%)   </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">   53 (14.4%)   </t>
+          <t xml:space="preserve">   49 (13.9%)   </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">    102 (15.7%)    </t>
+          <t xml:space="preserve">    98 (15.4%)     </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1202,27 +1202,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">   52 (2.53%)   </t>
+          <t xml:space="preserve">   49 (2.50%)   </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">   7 (0.94%)    </t>
+          <t xml:space="preserve">   6 (0.84%)    </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">   7 (2.34%)    </t>
+          <t xml:space="preserve">   6 (2.31%)    </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">   21 (5.72%)   </t>
+          <t xml:space="preserve">   20 (5.67%)   </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">    17 (2.62%)     </t>
+          <t xml:space="preserve">    17 (2.67%)     </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.013  </t>
+          <t xml:space="preserve">  0.041  </t>
         </is>
       </c>
     </row>
@@ -1276,27 +1276,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  252 (12.2%)   </t>
+          <t xml:space="preserve">  242 (12.3%)   </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">   91 (12.2%)   </t>
+          <t xml:space="preserve">   91 (12.7%)   </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">   47 (15.7%)   </t>
+          <t xml:space="preserve">   40 (15.4%)   </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">   47 (12.8%)   </t>
+          <t xml:space="preserve">   45 (12.7%)   </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    67 (10.3%)     </t>
+          <t xml:space="preserve">    66 (10.4%)     </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1313,22 +1313,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   8 (0.39%)    </t>
+          <t xml:space="preserve">   8 (0.41%)    </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   5 (0.67%)    </t>
+          <t xml:space="preserve">   5 (0.70%)    </t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   2 (0.67%)    </t>
+          <t xml:space="preserve">   2 (0.77%)    </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1 (0.27%)    </t>
+          <t xml:space="preserve">   1 (0.28%)    </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1350,27 +1350,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1044 (50.7%)  </t>
+          <t xml:space="preserve">  992 (50.5%)   </t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  389 (52.4%)   </t>
+          <t xml:space="preserve">  372 (52.1%)   </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  163 (54.5%)   </t>
+          <t xml:space="preserve">  139 (53.5%)   </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  174 (47.4%)   </t>
+          <t xml:space="preserve">  168 (47.6%)   </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">    318 (49.0%)    </t>
+          <t xml:space="preserve">    313 (49.2%)    </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1387,27 +1387,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  754 (36.6%)   </t>
+          <t xml:space="preserve">  721 (36.7%)   </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  258 (34.7%)   </t>
+          <t xml:space="preserve">  246 (34.5%)   </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">   87 (29.1%)   </t>
+          <t xml:space="preserve">   79 (30.4%)   </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  145 (39.5%)   </t>
+          <t xml:space="preserve">  139 (39.4%)   </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">    264 (40.7%)    </t>
+          <t xml:space="preserve">    257 (40.4%)    </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1461,27 +1461,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1008 (49.0%)  </t>
+          <t xml:space="preserve">  961 (49.0%)   </t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  433 (58.3%)   </t>
+          <t xml:space="preserve">  415 (58.1%)   </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  161 (53.8%)   </t>
+          <t xml:space="preserve">  143 (55.0%)   </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  145 (39.5%)   </t>
+          <t xml:space="preserve">  137 (38.8%)   </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">    269 (41.4%)    </t>
+          <t xml:space="preserve">    266 (41.8%)    </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1498,27 +1498,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  241 (11.7%)   </t>
+          <t xml:space="preserve">  219 (11.2%)   </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">   71 (9.56%)   </t>
+          <t xml:space="preserve">   68 (9.52%)   </t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">   99 (33.1%)   </t>
+          <t xml:space="preserve">   84 (32.3%)   </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">   19 (5.18%)   </t>
+          <t xml:space="preserve">   18 (5.10%)   </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">    52 (8.01%)     </t>
+          <t xml:space="preserve">    49 (7.70%)     </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1535,27 +1535,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  809 (39.3%)   </t>
+          <t xml:space="preserve">  783 (39.9%)   </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  239 (32.2%)   </t>
+          <t xml:space="preserve">  231 (32.4%)   </t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">   39 (13.0%)   </t>
+          <t xml:space="preserve">   33 (12.7%)   </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  203 (55.3%)   </t>
+          <t xml:space="preserve">  198 (56.1%)   </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">    328 (50.5%)    </t>
+          <t xml:space="preserve">    321 (50.5%)    </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1572,32 +1572,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.52 (0.95)   </t>
+          <t xml:space="preserve">  0.51 (0.95)   </t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.62 (0.95)   </t>
+          <t xml:space="preserve">  0.62 (0.96)   </t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.37 (0.76)   </t>
+          <t xml:space="preserve">  0.37 (0.74)   </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.53 (1.04)   </t>
+          <t xml:space="preserve">  0.51 (1.02)   </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">    0.46 (0.97)    </t>
+          <t xml:space="preserve">    0.45 (0.96)    </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve"> &lt;0.001  </t>
+          <t xml:space="preserve">  0.001  </t>
         </is>
       </c>
     </row>
@@ -1609,27 +1609,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  397 (19.3%)   </t>
+          <t xml:space="preserve">  374 (19.1%)   </t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  187 (25.2%)   </t>
+          <t xml:space="preserve">  180 (25.2%)   </t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   61 (20.4%)   </t>
+          <t xml:space="preserve">   51 (19.6%)   </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   42 (11.4%)   </t>
+          <t xml:space="preserve">   38 (10.8%)   </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">    107 (16.5%)    </t>
+          <t xml:space="preserve">    105 (16.5%)    </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1646,27 +1646,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  535 (26.0%)   </t>
+          <t xml:space="preserve">  505 (25.7%)   </t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  254 (34.2%)   </t>
+          <t xml:space="preserve">  243 (34.0%)   </t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">   75 (25.1%)   </t>
+          <t xml:space="preserve">   63 (24.2%)   </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">   73 (19.9%)   </t>
+          <t xml:space="preserve">   68 (19.3%)   </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">    133 (20.5%)    </t>
+          <t xml:space="preserve">    131 (20.6%)    </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>9.00 [5.00;15.0]</t>
+          <t>9.00 [5.00;15.2]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>17.0 [9.00;29.0]</t>
+          <t>17.0 [10.0;29.0]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>7.00 [3.00;15.5]</t>
+          <t>7.00 [3.00;15.0]</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1757,17 +1757,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">77.1 [52.1;100] </t>
+          <t xml:space="preserve">77.8 [52.9;100] </t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">86.7 [66.7;100] </t>
+          <t xml:space="preserve">87.2 [69.3;100] </t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>71.6 [57.1;85.1]</t>
+          <t>71.4 [57.1;85.0]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  66.7 [39.3;100]  </t>
+          <t xml:space="preserve">  66.0 [39.2;100]  </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>11.0 [5.00;18.0]</t>
+          <t>12.0 [5.00;18.0]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1868,27 +1868,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>46.2 [22.2;69.9]</t>
+          <t>45.9 [21.4;69.5]</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>53.3 [39.5;69.8]</t>
+          <t>53.3 [39.2;70.0]</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>50.0 [32.7;72.7]</t>
+          <t>50.0 [32.8;69.1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>16.7 [0.00;45.8]</t>
+          <t>16.7 [0.00;46.5]</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 40.0 [0.00;83.3]  </t>
+          <t xml:space="preserve"> 39.4 [0.00;85.7]  </t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1910,17 +1910,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>15.0 [10.0;27.0]</t>
+          <t>16.0 [10.0;27.0]</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>13.0 [8.00;21.5]</t>
+          <t>13.0 [8.00;21.2]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>8.00 [4.00;16.5]</t>
+          <t>8.00 [4.00;16.0]</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1947,12 +1947,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>34.0 [21.0;54.0]</t>
+          <t>34.0 [21.0;54.8]</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>30.0 [17.0;46.5]</t>
+          <t>31.0 [17.0;48.0]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1979,22 +1979,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">88.2 [72.7;100] </t>
+          <t xml:space="preserve">88.5 [73.3;100] </t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">93.8 [85.7;100] </t>
+          <t xml:space="preserve">94.0 [86.6;100] </t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>83.3 [73.5;91.7]</t>
+          <t>83.3 [74.2;91.4]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">83.3 [66.1;100] </t>
+          <t xml:space="preserve">83.3 [66.7;100] </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve"> &lt;0.001  </t>
+          <t xml:space="preserve">  0.001  </t>
         </is>
       </c>
     </row>
@@ -2127,27 +2127,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">   258 (156)    </t>
+          <t xml:space="preserve">   259 (156)    </t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">   252 (155)    </t>
+          <t xml:space="preserve">   254 (155)    </t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">   233 (156)    </t>
+          <t xml:space="preserve">   229 (156)    </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">   252 (159)    </t>
+          <t xml:space="preserve">   253 (160)    </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">     281 (154)     </t>
+          <t xml:space="preserve">     282 (154)     </t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2164,32 +2164,32 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">   294 (146)    </t>
+          <t xml:space="preserve">   295 (146)    </t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">   289 (146)    </t>
+          <t xml:space="preserve">   291 (145)    </t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">   277 (150)    </t>
+          <t xml:space="preserve">   275 (150)    </t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">   293 (152)    </t>
+          <t xml:space="preserve">   294 (152)    </t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">     308 (141)     </t>
+          <t xml:space="preserve">     307 (142)     </t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.014  </t>
+          <t xml:space="preserve">  0.024  </t>
         </is>
       </c>
     </row>
@@ -2206,878 +2206,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">   314 (138)    </t>
+          <t xml:space="preserve">   316 (137)    </t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">   312 (139)    </t>
+          <t xml:space="preserve">   307 (143)    </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">   328 (133)    </t>
+          <t xml:space="preserve">   327 (134)    </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">     339 (125)     </t>
+          <t xml:space="preserve">     339 (126)     </t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.001  </t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>SEM_num_cat3, N (%):</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                </t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                </t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                </t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                </t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   </t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> &lt;0.001  </t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    0</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  898 (43.6%)   </t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  300 (40.4%)   </t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  106 (35.5%)   </t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  154 (42.0%)   </t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    338 (52.1%)    </t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         </t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    1</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  480 (23.3%)   </t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  177 (23.8%)   </t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   82 (27.4%)   </t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   80 (21.8%)   </t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    141 (21.7%)    </t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         </t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    2+</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  680 (33.0%)   </t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  266 (35.8%)   </t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  111 (37.1%)   </t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  133 (36.2%)   </t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    170 (26.2%)    </t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         </t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>emergency_visits_cat3, N (%):</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                </t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                </t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                </t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                </t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   </t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  0.006  </t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    0</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  986 (47.9%)   </t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  342 (46.0%)   </t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  125 (41.8%)   </t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  168 (45.8%)   </t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    351 (54.1%)    </t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         </t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    1</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  453 (22.0%)   </t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  173 (23.3%)   </t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   69 (23.1%)   </t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   78 (21.3%)   </t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    133 (20.5%)    </t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         </t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    2+</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  619 (30.1%)   </t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  228 (30.7%)   </t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  105 (35.1%)   </t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  121 (33.0%)   </t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    165 (25.4%)    </t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         </t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>INGRES_num_cat3, N (%):</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                </t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                </t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                </t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                </t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   </t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> &lt;0.001  </t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    0</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1359 (66.0%)  </t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  458 (61.6%)   </t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  184 (61.5%)   </t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  250 (68.1%)   </t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    467 (72.0%)    </t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         </t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    1</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  380 (18.5%)   </t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  168 (22.6%)   </t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   57 (19.1%)   </t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   54 (14.7%)   </t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    101 (15.6%)    </t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         </t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    2+</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  319 (15.5%)   </t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  117 (15.7%)   </t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   58 (19.4%)   </t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   63 (17.2%)   </t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    81 (12.5%)     </t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         </t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Exitus_cat3, N (%): 'Missing'</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2058 (100%)   </t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   743 (100%)   </t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   299 (100%)   </t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   367 (100%)   </t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    649 (100%)     </t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    .    </t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>SEM_num_cat2, N (%):</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                </t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                </t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                </t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                </t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   </t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> &lt;0.001  </t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    0</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  898 (43.6%)   </t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  300 (40.4%)   </t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  106 (35.5%)   </t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  154 (42.0%)   </t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    338 (52.1%)    </t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         </t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    1+</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1160 (56.4%)  </t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  443 (59.6%)   </t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  193 (64.5%)   </t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  213 (58.0%)   </t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    311 (47.9%)    </t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         </t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>emergency_visits_cat2, N (%):</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                </t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                </t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                </t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                </t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   </t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  0.001  </t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    0</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  986 (47.9%)   </t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  342 (46.0%)   </t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  125 (41.8%)   </t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  168 (45.8%)   </t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    351 (54.1%)    </t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         </t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    1+</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1072 (52.1%)  </t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  401 (54.0%)   </t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  174 (58.2%)   </t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  199 (54.2%)   </t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    298 (45.9%)    </t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         </t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>INGRES_num_cat2, N (%):</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                </t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                </t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                </t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                </t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   </t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> &lt;0.001  </t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    0</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1359 (66.0%)  </t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  458 (61.6%)   </t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  184 (61.5%)   </t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  250 (68.1%)   </t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    467 (72.0%)    </t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         </t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    1+</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  699 (34.0%)   </t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  285 (38.4%)   </t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  115 (38.5%)   </t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  117 (31.9%)   </t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    182 (28.0%)    </t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         </t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Exitus_cat2, N (%): 'Missing'</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2058 (100%)   </t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   743 (100%)   </t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   299 (100%)   </t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   367 (100%)   </t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    649 (100%)     </t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    .    </t>
+          <t xml:space="preserve">  0.002  </t>
         </is>
       </c>
     </row>
